--- a/data_sources/products.xlsx
+++ b/data_sources/products.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\тестпапка\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{118E424D-929A-4E28-99B2-C5C6FF079529}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33BD8063-2D8A-4877-B492-410953750A15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{66CCEC8E-7F34-46B2-94A3-C485FEA95E42}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="31">
   <si>
     <t>Код</t>
   </si>
@@ -98,9 +98,6 @@
     <t>ФИО</t>
   </si>
   <si>
-    <t>Буров Велорий</t>
-  </si>
-  <si>
     <t>Горячий цех</t>
   </si>
   <si>
@@ -108,6 +105,30 @@
   </si>
   <si>
     <t>Майонез ЭФКО ВВ</t>
+  </si>
+  <si>
+    <t>Фаршированные кабачки с грузинским соусом</t>
+  </si>
+  <si>
+    <t>Иван Иванов</t>
+  </si>
+  <si>
+    <t>Нет</t>
+  </si>
+  <si>
+    <t>кг,шт,порц</t>
+  </si>
+  <si>
+    <t>Пётр Петров</t>
+  </si>
+  <si>
+    <t>Василий Васильев</t>
+  </si>
+  <si>
+    <t>Заготовочный цех</t>
+  </si>
+  <si>
+    <t>Не будет отображаться</t>
   </si>
 </sst>
 </file>
@@ -480,6 +501,8 @@
   <cols>
     <col min="2" max="2" width="31.7109375" customWidth="1"/>
     <col min="3" max="3" width="16.5703125" customWidth="1"/>
+    <col min="4" max="4" width="11" customWidth="1"/>
+    <col min="6" max="6" width="21.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
@@ -530,7 +553,7 @@
         <v>18</v>
       </c>
       <c r="D3" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -583,8 +606,8 @@
       <c r="D6" t="s">
         <v>7</v>
       </c>
-      <c r="E6" t="s">
-        <v>8</v>
+      <c r="F6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -652,7 +675,10 @@
         <v>17</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>25</v>
+      </c>
+      <c r="F10" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -678,7 +704,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C12">
         <v>336</v>
@@ -692,6 +718,21 @@
       <c r="I12" s="2"/>
     </row>
     <row r="13" spans="1:12">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13">
+        <v>12</v>
+      </c>
+      <c r="D13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
       <c r="I13" s="2"/>
     </row>
     <row r="14" spans="1:12">
@@ -719,8 +760,8 @@
       <c r="I21" s="2"/>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K12:K21 D2:D12" xr:uid="{75D836D7-18FB-4F4E-BB8C-914D53D26E5B}">
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K12:K21" xr:uid="{75D836D7-18FB-4F4E-BB8C-914D53D26E5B}">
       <mc:AlternateContent xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
         <mc:Choice Requires="x12ac">
           <x12ac:list>"кг,шт",кг,шт</x12ac:list>
@@ -730,8 +771,18 @@
         </mc:Fallback>
       </mc:AlternateContent>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L11:L21 E1:E12" xr:uid="{71D4CA19-8366-4B2E-87F8-1ABE1D5BB112}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L11:L21 E1:E13" xr:uid="{71D4CA19-8366-4B2E-87F8-1ABE1D5BB112}">
       <formula1>"Да,Нет"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D13" xr:uid="{3EAD37E3-F23F-475D-9EEF-314647C92E35}">
+      <mc:AlternateContent xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+        <mc:Choice Requires="x12ac">
+          <x12ac:list>кг,шт,порц,,"кг,шт,порц","кг,шт","кг,порц","шт,порц"</x12ac:list>
+        </mc:Choice>
+        <mc:Fallback>
+          <formula1>"кг,шт,порц,,кг,шт,порц,кг,шт,кг,порц,шт,порц"</formula1>
+        </mc:Fallback>
+      </mc:AlternateContent>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -744,7 +795,7 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.85546875" customWidth="1"/>
-    <col min="2" max="2" width="7" customWidth="1"/>
+    <col min="2" max="2" width="9.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -757,19 +808,27 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
+      <c r="A3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
+      <c r="A4" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="3"/>
@@ -803,23 +862,42 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD1E4A79-849E-4F0A-972D-8848F8539A9D}">
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1">
+        <v>21</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1:B3" xr:uid="{AD819B4B-DB90-4F13-B4BA-B86D99DC3C4C}">
+      <formula1>"Да,Нет"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>